--- a/OUTPUT_REPORT/report_data.xlsx
+++ b/OUTPUT_REPORT/report_data.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Disagreement</t>
+          <t>Alignment</t>
         </is>
       </c>
     </row>
@@ -600,8 +600,10 @@
       <c r="R2" t="n">
         <v>0.9758096761295482</v>
       </c>
-      <c r="S2" t="b">
-        <v>1</v>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -679,8 +681,10 @@
       <c r="R3" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="S3" t="b">
-        <v>0</v>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -762,8 +766,10 @@
       <c r="R4" t="n">
         <v>0.09876049580167934</v>
       </c>
-      <c r="S4" t="b">
-        <v>1</v>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -845,8 +851,10 @@
       <c r="R5" t="n">
         <v>0.1857257097161136</v>
       </c>
-      <c r="S5" t="b">
-        <v>1</v>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -924,8 +932,10 @@
       <c r="R6" t="n">
         <v>0.6139544182327069</v>
       </c>
-      <c r="S6" t="b">
-        <v>0</v>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1003,8 +1013,10 @@
       <c r="R7" t="n">
         <v>0.7137145141943222</v>
       </c>
-      <c r="S7" t="b">
-        <v>1</v>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1082,8 +1094,10 @@
       <c r="R8" t="n">
         <v>0.8348660535785686</v>
       </c>
-      <c r="S8" t="b">
-        <v>1</v>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1161,8 +1175,10 @@
       <c r="R9" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S9" t="b">
-        <v>0</v>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1240,8 +1256,10 @@
       <c r="R10" t="n">
         <v>0.8222710915633746</v>
       </c>
-      <c r="S10" t="b">
-        <v>0</v>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1319,8 +1337,10 @@
       <c r="R11" t="n">
         <v>0.4586165533786486</v>
       </c>
-      <c r="S11" t="b">
-        <v>0</v>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1398,8 +1418,10 @@
       <c r="R12" t="n">
         <v>0.9390243902439024</v>
       </c>
-      <c r="S12" t="b">
-        <v>1</v>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1477,8 +1499,10 @@
       <c r="R13" t="n">
         <v>0.05597760895641746</v>
       </c>
-      <c r="S13" t="b">
-        <v>1</v>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1556,8 +1580,10 @@
       <c r="R14" t="n">
         <v>0.4202319072371051</v>
       </c>
-      <c r="S14" t="b">
-        <v>1</v>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1635,8 +1661,10 @@
       <c r="R15" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="S15" t="b">
-        <v>0</v>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1714,8 +1742,10 @@
       <c r="R16" t="n">
         <v>0.4494202319072371</v>
       </c>
-      <c r="S16" t="b">
-        <v>0</v>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1793,8 +1823,10 @@
       <c r="R17" t="n">
         <v>0.4878048780487805</v>
       </c>
-      <c r="S17" t="b">
-        <v>1</v>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1872,8 +1904,10 @@
       <c r="R18" t="n">
         <v>0.01239504198320673</v>
       </c>
-      <c r="S18" t="b">
-        <v>1</v>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1951,8 +1985,10 @@
       <c r="R19" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S19" t="b">
-        <v>1</v>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2030,8 +2066,10 @@
       <c r="R20" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S20" t="b">
-        <v>1</v>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2109,8 +2147,10 @@
       <c r="R21" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S21" t="b">
-        <v>1</v>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2188,8 +2228,10 @@
       <c r="R22" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S22" t="b">
-        <v>1</v>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2267,8 +2309,10 @@
       <c r="R23" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S23" t="b">
-        <v>1</v>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2346,8 +2390,10 @@
       <c r="R24" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S24" t="b">
-        <v>1</v>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2425,8 +2471,10 @@
       <c r="R25" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S25" t="b">
-        <v>1</v>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2504,8 +2552,10 @@
       <c r="R26" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S26" t="b">
-        <v>1</v>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2583,8 +2633,10 @@
       <c r="R27" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="S27" t="b">
-        <v>0</v>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2662,8 +2714,10 @@
       <c r="R28" t="n">
         <v>0.9174330267892843</v>
       </c>
-      <c r="S28" t="b">
-        <v>0</v>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2741,8 +2795,10 @@
       <c r="R29" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S29" t="b">
-        <v>0</v>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2820,8 +2876,10 @@
       <c r="R30" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S30" t="b">
-        <v>0</v>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2899,8 +2957,10 @@
       <c r="R31" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S31" t="b">
-        <v>0</v>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2978,8 +3038,10 @@
       <c r="R32" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S32" t="b">
-        <v>0</v>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -3057,8 +3119,10 @@
       <c r="R33" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S33" t="b">
-        <v>0</v>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -3136,8 +3200,10 @@
       <c r="R34" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S34" t="b">
-        <v>0</v>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -3215,8 +3281,10 @@
       <c r="R35" t="n">
         <v>0.9816073570571772</v>
       </c>
-      <c r="S35" t="b">
-        <v>1</v>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -3294,8 +3362,10 @@
       <c r="R36" t="n">
         <v>0.9992003198720512</v>
       </c>
-      <c r="S36" t="b">
-        <v>0</v>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3373,8 +3443,10 @@
       <c r="R37" t="n">
         <v>0.771891243502599</v>
       </c>
-      <c r="S37" t="b">
-        <v>0</v>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3452,8 +3524,10 @@
       <c r="R38" t="n">
         <v>0.1529388244702119</v>
       </c>
-      <c r="S38" t="b">
-        <v>1</v>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -3531,8 +3605,10 @@
       <c r="R39" t="n">
         <v>0.1529388244702119</v>
       </c>
-      <c r="S39" t="b">
-        <v>1</v>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -3610,8 +3686,10 @@
       <c r="R40" t="n">
         <v>0.9008396641343462</v>
       </c>
-      <c r="S40" t="b">
-        <v>0</v>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -3689,8 +3767,10 @@
       <c r="R41" t="n">
         <v>0.122750899640144</v>
       </c>
-      <c r="S41" t="b">
-        <v>0</v>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3768,8 +3848,10 @@
       <c r="R42" t="n">
         <v>0.122750899640144</v>
       </c>
-      <c r="S42" t="b">
-        <v>0</v>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3847,8 +3929,10 @@
       <c r="R43" t="n">
         <v>0.4972011195521792</v>
       </c>
-      <c r="S43" t="b">
-        <v>0</v>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3926,8 +4010,10 @@
       <c r="R44" t="n">
         <v>0.4972011195521792</v>
       </c>
-      <c r="S44" t="b">
-        <v>0</v>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -4005,8 +4091,10 @@
       <c r="R45" t="n">
         <v>0.9194322271091564</v>
       </c>
-      <c r="S45" t="b">
-        <v>1</v>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -4084,8 +4172,10 @@
       <c r="R46" t="n">
         <v>0.9644142343062775</v>
       </c>
-      <c r="S46" t="b">
-        <v>1</v>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -4163,8 +4253,10 @@
       <c r="R47" t="n">
         <v>0.9992003198720512</v>
       </c>
-      <c r="S47" t="b">
-        <v>0</v>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -4242,8 +4334,10 @@
       <c r="R48" t="n">
         <v>0.8408636545381847</v>
       </c>
-      <c r="S48" t="b">
-        <v>0</v>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4321,8 +4415,10 @@
       <c r="R49" t="n">
         <v>0.8250699720111956</v>
       </c>
-      <c r="S49" t="b">
-        <v>0</v>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4400,8 +4496,10 @@
       <c r="R50" t="n">
         <v>0.9126349460215913</v>
       </c>
-      <c r="S50" t="b">
-        <v>1</v>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -4479,8 +4577,10 @@
       <c r="R51" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S51" t="b">
-        <v>0</v>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -4558,8 +4658,10 @@
       <c r="R52" t="n">
         <v>0.6477409036385446</v>
       </c>
-      <c r="S52" t="b">
-        <v>0</v>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -4637,8 +4739,10 @@
       <c r="R53" t="n">
         <v>0.003998400639744104</v>
       </c>
-      <c r="S53" t="b">
-        <v>1</v>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -4716,8 +4820,10 @@
       <c r="R54" t="n">
         <v>0.003998400639744104</v>
       </c>
-      <c r="S54" t="b">
-        <v>1</v>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4795,8 +4901,10 @@
       <c r="R55" t="n">
         <v>0.003998400639744104</v>
       </c>
-      <c r="S55" t="b">
-        <v>1</v>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4874,8 +4982,10 @@
       <c r="R56" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S56" t="b">
-        <v>1</v>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -4953,8 +5063,10 @@
       <c r="R57" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S57" t="b">
-        <v>1</v>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -5032,8 +5144,10 @@
       <c r="R58" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S58" t="b">
-        <v>1</v>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -5111,8 +5225,10 @@
       <c r="R59" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S59" t="b">
-        <v>1</v>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -5190,8 +5306,10 @@
       <c r="R60" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S60" t="b">
-        <v>1</v>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -5269,8 +5387,10 @@
       <c r="R61" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S61" t="b">
-        <v>1</v>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -5348,8 +5468,10 @@
       <c r="R62" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S62" t="b">
-        <v>1</v>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -5427,8 +5549,10 @@
       <c r="R63" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S63" t="b">
-        <v>1</v>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -5506,8 +5630,10 @@
       <c r="R64" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S64" t="b">
-        <v>1</v>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -5585,8 +5711,10 @@
       <c r="R65" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S65" t="b">
-        <v>1</v>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -5664,8 +5792,10 @@
       <c r="R66" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S66" t="b">
-        <v>1</v>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -5743,8 +5873,10 @@
       <c r="R67" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S67" t="b">
-        <v>1</v>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -5822,8 +5954,10 @@
       <c r="R68" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S68" t="b">
-        <v>1</v>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -5901,8 +6035,10 @@
       <c r="R69" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S69" t="b">
-        <v>1</v>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -5980,8 +6116,10 @@
       <c r="R70" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S70" t="b">
-        <v>1</v>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -6059,8 +6197,10 @@
       <c r="R71" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S71" t="b">
-        <v>1</v>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -6138,8 +6278,10 @@
       <c r="R72" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S72" t="b">
-        <v>1</v>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -6217,8 +6359,10 @@
       <c r="R73" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S73" t="b">
-        <v>1</v>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -6296,8 +6440,10 @@
       <c r="R74" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="S74" t="b">
-        <v>0</v>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -6375,8 +6521,10 @@
       <c r="R75" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="S75" t="b">
-        <v>0</v>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -6454,8 +6602,10 @@
       <c r="R76" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="S76" t="b">
-        <v>0</v>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -6533,8 +6683,10 @@
       <c r="R77" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="S77" t="b">
-        <v>0</v>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -6612,8 +6764,10 @@
       <c r="R78" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S78" t="b">
-        <v>0</v>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -6691,8 +6845,10 @@
       <c r="R79" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S79" t="b">
-        <v>0</v>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -6770,8 +6926,10 @@
       <c r="R80" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S80" t="b">
-        <v>0</v>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -6849,8 +7007,10 @@
       <c r="R81" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S81" t="b">
-        <v>0</v>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -6928,8 +7088,10 @@
       <c r="R82" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S82" t="b">
-        <v>0</v>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -7007,8 +7169,10 @@
       <c r="R83" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S83" t="b">
-        <v>0</v>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -7086,8 +7250,10 @@
       <c r="R84" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S84" t="b">
-        <v>0</v>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -7165,8 +7331,10 @@
       <c r="R85" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S85" t="b">
-        <v>0</v>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -7244,8 +7412,10 @@
       <c r="R86" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S86" t="b">
-        <v>0</v>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -7323,8 +7493,10 @@
       <c r="R87" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S87" t="b">
-        <v>0</v>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -7402,8 +7574,10 @@
       <c r="R88" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S88" t="b">
-        <v>0</v>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -7481,8 +7655,10 @@
       <c r="R89" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S89" t="b">
-        <v>0</v>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -7560,8 +7736,10 @@
       <c r="R90" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S90" t="b">
-        <v>0</v>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -7639,8 +7817,10 @@
       <c r="R91" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S91" t="b">
-        <v>0</v>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -7718,8 +7898,10 @@
       <c r="R92" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S92" t="b">
-        <v>0</v>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -7797,8 +7979,10 @@
       <c r="R93" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S93" t="b">
-        <v>1</v>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -7876,8 +8060,10 @@
       <c r="R94" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S94" t="b">
-        <v>1</v>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -7955,8 +8141,10 @@
       <c r="R95" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S95" t="b">
-        <v>1</v>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -8034,8 +8222,10 @@
       <c r="R96" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S96" t="b">
-        <v>1</v>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -8113,8 +8303,10 @@
       <c r="R97" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S97" t="b">
-        <v>1</v>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -8192,8 +8384,10 @@
       <c r="R98" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S98" t="b">
-        <v>1</v>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -8271,8 +8465,10 @@
       <c r="R99" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="S99" t="b">
-        <v>0</v>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -8350,8 +8546,10 @@
       <c r="R100" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="S100" t="b">
-        <v>0</v>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -8429,8 +8627,10 @@
       <c r="R101" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="S101" t="b">
-        <v>0</v>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -8508,8 +8708,10 @@
       <c r="R102" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="S102" t="b">
-        <v>0</v>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -8587,8 +8789,10 @@
       <c r="R103" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="S103" t="b">
-        <v>0</v>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -8666,8 +8870,10 @@
       <c r="R104" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="S104" t="b">
-        <v>1</v>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -8745,8 +8951,10 @@
       <c r="R105" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="S105" t="b">
-        <v>1</v>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -8824,8 +9032,10 @@
       <c r="R106" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S106" t="b">
-        <v>1</v>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -8903,8 +9113,10 @@
       <c r="R107" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S107" t="b">
-        <v>0</v>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -8982,8 +9194,10 @@
       <c r="R108" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S108" t="b">
-        <v>0</v>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -9061,8 +9275,10 @@
       <c r="R109" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S109" t="b">
-        <v>0</v>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -9140,8 +9356,10 @@
       <c r="R110" t="n">
         <v>0.8158736505397841</v>
       </c>
-      <c r="S110" t="b">
-        <v>1</v>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -9219,8 +9437,10 @@
       <c r="R111" t="n">
         <v>0.1157536985205918</v>
       </c>
-      <c r="S111" t="b">
-        <v>1</v>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -9298,8 +9518,10 @@
       <c r="R112" t="n">
         <v>0.2850859656137545</v>
       </c>
-      <c r="S112" t="b">
-        <v>1</v>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -9377,8 +9599,10 @@
       <c r="R113" t="n">
         <v>0.4456217512994802</v>
       </c>
-      <c r="S113" t="b">
-        <v>0</v>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -9456,8 +9680,10 @@
       <c r="R114" t="n">
         <v>0.3396641343462615</v>
       </c>
-      <c r="S114" t="b">
-        <v>0</v>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -9535,8 +9761,10 @@
       <c r="R115" t="n">
         <v>0.3410635745701719</v>
       </c>
-      <c r="S115" t="b">
-        <v>1</v>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -9614,8 +9842,10 @@
       <c r="R116" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="S116" t="b">
-        <v>0</v>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -9697,8 +9927,10 @@
       <c r="R117" t="n">
         <v>0.2636945221911235</v>
       </c>
-      <c r="S117" t="b">
-        <v>1</v>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -9776,8 +10008,10 @@
       <c r="R118" t="n">
         <v>0.9646141543382647</v>
       </c>
-      <c r="S118" t="b">
-        <v>0</v>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -9855,8 +10089,10 @@
       <c r="R119" t="n">
         <v>0.9770091963214714</v>
       </c>
-      <c r="S119" t="b">
-        <v>1</v>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -9934,8 +10170,10 @@
       <c r="R120" t="n">
         <v>0.9666133546581368</v>
       </c>
-      <c r="S120" t="b">
-        <v>0</v>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -10013,8 +10251,10 @@
       <c r="R121" t="n">
         <v>0.1897241103558577</v>
       </c>
-      <c r="S121" t="b">
-        <v>0</v>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -10096,8 +10336,10 @@
       <c r="R122" t="n">
         <v>0.3104758096761295</v>
       </c>
-      <c r="S122" t="b">
-        <v>1</v>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -10179,8 +10421,10 @@
       <c r="R123" t="n">
         <v>0.9908036785285885</v>
       </c>
-      <c r="S123" t="b">
-        <v>0</v>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -10262,8 +10506,10 @@
       <c r="R124" t="n">
         <v>0.1221511395441823</v>
       </c>
-      <c r="S124" t="b">
-        <v>0</v>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -10345,8 +10591,10 @@
       <c r="R125" t="n">
         <v>0.7127149140343862</v>
       </c>
-      <c r="S125" t="b">
-        <v>1</v>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -10428,8 +10676,10 @@
       <c r="R126" t="n">
         <v>0.0331867253098761</v>
       </c>
-      <c r="S126" t="b">
-        <v>1</v>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -10511,8 +10761,10 @@
       <c r="R127" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="S127" t="b">
-        <v>0</v>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -10594,8 +10846,10 @@
       <c r="R128" t="n">
         <v>0.458016793282687</v>
       </c>
-      <c r="S128" t="b">
-        <v>0</v>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -10677,8 +10931,10 @@
       <c r="R129" t="n">
         <v>0.00299880047980805</v>
       </c>
-      <c r="S129" t="b">
-        <v>0</v>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -10760,8 +11016,10 @@
       <c r="R130" t="n">
         <v>0.06237504998000798</v>
       </c>
-      <c r="S130" t="b">
-        <v>1</v>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -10843,8 +11101,10 @@
       <c r="R131" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="S131" t="b">
-        <v>0</v>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -10926,8 +11186,10 @@
       <c r="R132" t="n">
         <v>0.02439024390243905</v>
       </c>
-      <c r="S132" t="b">
-        <v>0</v>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -11009,8 +11271,10 @@
       <c r="R133" t="n">
         <v>0.3932427029188325</v>
       </c>
-      <c r="S133" t="b">
-        <v>1</v>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -11092,8 +11356,10 @@
       <c r="R134" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S134" t="b">
-        <v>1</v>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -11175,8 +11441,10 @@
       <c r="R135" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S135" t="b">
-        <v>1</v>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -11258,8 +11526,10 @@
       <c r="R136" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="S136" t="b">
-        <v>0</v>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -11341,8 +11611,10 @@
       <c r="R137" t="n">
         <v>0.001799280287884897</v>
       </c>
-      <c r="S137" t="b">
-        <v>0</v>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -11424,8 +11696,10 @@
       <c r="R138" t="n">
         <v>0.001799280287884897</v>
       </c>
-      <c r="S138" t="b">
-        <v>0</v>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -11507,8 +11781,10 @@
       <c r="R139" t="n">
         <v>0.9780087964814075</v>
       </c>
-      <c r="S139" t="b">
-        <v>0</v>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -11594,8 +11870,10 @@
       <c r="R140" t="n">
         <v>0.6681327469012395</v>
       </c>
-      <c r="S140" t="b">
-        <v>1</v>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -11677,8 +11955,10 @@
       <c r="R141" t="n">
         <v>0.9198320671731307</v>
       </c>
-      <c r="S141" t="b">
-        <v>0</v>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -11764,8 +12044,10 @@
       <c r="R142" t="n">
         <v>0.272890843662535</v>
       </c>
-      <c r="S142" t="b">
-        <v>1</v>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -11847,8 +12129,10 @@
       <c r="R143" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="S143" t="b">
-        <v>0</v>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -11934,8 +12218,10 @@
       <c r="R144" t="n">
         <v>0.01439424230307873</v>
       </c>
-      <c r="S144" t="b">
-        <v>1</v>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -12021,8 +12307,10 @@
       <c r="R145" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S145" t="b">
-        <v>1</v>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -12108,8 +12396,10 @@
       <c r="R146" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S146" t="b">
-        <v>1</v>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -12195,8 +12485,10 @@
       <c r="R147" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S147" t="b">
-        <v>1</v>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -12282,8 +12574,10 @@
       <c r="R148" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S148" t="b">
-        <v>1</v>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -12361,8 +12655,10 @@
       <c r="R149" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="S149" t="b">
-        <v>0</v>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -12424,8 +12720,10 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="b">
-        <v>1</v>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -12503,8 +12801,10 @@
       <c r="R151" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="S151" t="b">
-        <v>1</v>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -12582,8 +12882,10 @@
       <c r="R152" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S152" t="b">
-        <v>0</v>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -12661,8 +12963,10 @@
       <c r="R153" t="n">
         <v>0.5675729708116753</v>
       </c>
-      <c r="S153" t="b">
-        <v>0</v>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -12740,8 +13044,10 @@
       <c r="R154" t="n">
         <v>0.4290283886445422</v>
       </c>
-      <c r="S154" t="b">
-        <v>0</v>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -12823,8 +13129,10 @@
       <c r="R155" t="n">
         <v>0.6381447421031587</v>
       </c>
-      <c r="S155" t="b">
-        <v>1</v>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -12902,8 +13210,10 @@
       <c r="R156" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="S156" t="b">
-        <v>0</v>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -12981,8 +13291,10 @@
       <c r="R157" t="n">
         <v>0.5683726509396241</v>
       </c>
-      <c r="S157" t="b">
-        <v>0</v>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -13064,8 +13376,10 @@
       <c r="R158" t="n">
         <v>0.9602159136345462</v>
       </c>
-      <c r="S158" t="b">
-        <v>1</v>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -13147,8 +13461,10 @@
       <c r="R159" t="n">
         <v>0.8310675729708117</v>
       </c>
-      <c r="S159" t="b">
-        <v>1</v>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -13230,8 +13546,10 @@
       <c r="R160" t="n">
         <v>0.4626149540183926</v>
       </c>
-      <c r="S160" t="b">
-        <v>1</v>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -13313,8 +13631,10 @@
       <c r="R161" t="n">
         <v>0.01459416233506594</v>
       </c>
-      <c r="S161" t="b">
-        <v>1</v>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -13396,8 +13716,10 @@
       <c r="R162" t="n">
         <v>0.01459416233506594</v>
       </c>
-      <c r="S162" t="b">
-        <v>1</v>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -13479,8 +13801,10 @@
       <c r="R163" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S163" t="b">
-        <v>1</v>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -13562,8 +13886,10 @@
       <c r="R164" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S164" t="b">
-        <v>1</v>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -13645,8 +13971,10 @@
       <c r="R165" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S165" t="b">
-        <v>1</v>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -13728,8 +14056,10 @@
       <c r="R166" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S166" t="b">
-        <v>1</v>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -13811,8 +14141,10 @@
       <c r="R167" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="S167" t="b">
-        <v>0</v>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -13894,8 +14226,10 @@
       <c r="R168" t="n">
         <v>0.383046781287485</v>
       </c>
-      <c r="S168" t="b">
-        <v>0</v>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -13977,8 +14311,10 @@
       <c r="R169" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S169" t="b">
-        <v>0</v>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -14060,8 +14396,10 @@
       <c r="R170" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S170" t="b">
-        <v>0</v>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -14143,8 +14481,10 @@
       <c r="R171" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S171" t="b">
-        <v>0</v>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -14226,8 +14566,10 @@
       <c r="R172" t="n">
         <v>0.4972011195521792</v>
       </c>
-      <c r="S172" t="b">
-        <v>1</v>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -14309,8 +14651,10 @@
       <c r="R173" t="n">
         <v>0.9978008796481408</v>
       </c>
-      <c r="S173" t="b">
-        <v>0</v>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -14392,8 +14736,10 @@
       <c r="R174" t="n">
         <v>0.2726909236305478</v>
       </c>
-      <c r="S174" t="b">
-        <v>0</v>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -14475,8 +14821,10 @@
       <c r="R175" t="n">
         <v>0.8760495801679329</v>
       </c>
-      <c r="S175" t="b">
-        <v>1</v>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -14558,8 +14906,10 @@
       <c r="R176" t="n">
         <v>0.8164734106357456</v>
       </c>
-      <c r="S176" t="b">
-        <v>0</v>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -14625,8 +14975,10 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="b">
-        <v>1</v>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -14708,8 +15060,10 @@
       <c r="R178" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S178" t="b">
-        <v>0</v>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -14791,8 +15145,10 @@
       <c r="R179" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="S179" t="b">
-        <v>1</v>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -14874,8 +15230,10 @@
       <c r="R180" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="S180" t="b">
-        <v>1</v>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -14957,8 +15315,10 @@
       <c r="R181" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="S181" t="b">
-        <v>1</v>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -15040,8 +15400,10 @@
       <c r="R182" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="S182" t="b">
-        <v>0</v>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -15123,8 +15485,10 @@
       <c r="R183" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S183" t="b">
-        <v>0</v>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -15206,8 +15570,10 @@
       <c r="R184" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S184" t="b">
-        <v>0</v>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -15289,8 +15655,10 @@
       <c r="R185" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S185" t="b">
-        <v>0</v>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -15372,8 +15740,10 @@
       <c r="R186" t="n">
         <v>0.01979208316673331</v>
       </c>
-      <c r="S186" t="b">
-        <v>1</v>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -15455,8 +15825,10 @@
       <c r="R187" t="n">
         <v>0.1931227508996401</v>
       </c>
-      <c r="S187" t="b">
-        <v>1</v>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -15534,8 +15906,10 @@
       <c r="R188" t="n">
         <v>0.9952019192323071</v>
       </c>
-      <c r="S188" t="b">
-        <v>0</v>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -15613,8 +15987,10 @@
       <c r="R189" t="n">
         <v>0.2992802878848461</v>
       </c>
-      <c r="S189" t="b">
-        <v>0</v>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -15696,8 +16072,10 @@
       <c r="R190" t="n">
         <v>0.0645741703318673</v>
       </c>
-      <c r="S190" t="b">
-        <v>1</v>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -15775,8 +16153,10 @@
       <c r="R191" t="n">
         <v>0.9966013594562175</v>
       </c>
-      <c r="S191" t="b">
-        <v>0</v>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -15858,8 +16238,10 @@
       <c r="R192" t="n">
         <v>0.1133546581367453</v>
       </c>
-      <c r="S192" t="b">
-        <v>1</v>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -15941,8 +16323,10 @@
       <c r="R193" t="n">
         <v>0.1133546581367453</v>
       </c>
-      <c r="S193" t="b">
-        <v>1</v>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -16024,8 +16408,10 @@
       <c r="R194" t="n">
         <v>0.7612954818072771</v>
       </c>
-      <c r="S194" t="b">
-        <v>0</v>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -16107,8 +16493,10 @@
       <c r="R195" t="n">
         <v>0.04058376649340267</v>
       </c>
-      <c r="S195" t="b">
-        <v>0</v>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -16190,8 +16578,10 @@
       <c r="R196" t="n">
         <v>0.04058376649340267</v>
       </c>
-      <c r="S196" t="b">
-        <v>0</v>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -16273,8 +16663,10 @@
       <c r="R197" t="n">
         <v>0.04058376649340267</v>
       </c>
-      <c r="S197" t="b">
-        <v>0</v>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -16352,8 +16744,10 @@
       <c r="R198" t="n">
         <v>0.7522990803678529</v>
       </c>
-      <c r="S198" t="b">
-        <v>1</v>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -16431,8 +16825,10 @@
       <c r="R199" t="n">
         <v>0.7522990803678529</v>
       </c>
-      <c r="S199" t="b">
-        <v>1</v>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -16510,8 +16906,10 @@
       <c r="R200" t="n">
         <v>0.9840063974410236</v>
       </c>
-      <c r="S200" t="b">
-        <v>0</v>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -16589,8 +16987,10 @@
       <c r="R201" t="n">
         <v>0.9294282287085166</v>
       </c>
-      <c r="S201" t="b">
-        <v>0</v>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -16668,8 +17068,10 @@
       <c r="R202" t="n">
         <v>0.4598160735705717</v>
       </c>
-      <c r="S202" t="b">
-        <v>0</v>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -16751,8 +17153,10 @@
       <c r="R203" t="n">
         <v>0.2085165933626549</v>
       </c>
-      <c r="S203" t="b">
-        <v>1</v>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -16830,8 +17234,10 @@
       <c r="R204" t="n">
         <v>0.1951219512195121</v>
       </c>
-      <c r="S204" t="b">
-        <v>0</v>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -16909,8 +17315,10 @@
       <c r="R205" t="n">
         <v>0.05597760895641746</v>
       </c>
-      <c r="S205" t="b">
-        <v>1</v>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -16988,8 +17396,10 @@
       <c r="R206" t="n">
         <v>0.9992003198720512</v>
       </c>
-      <c r="S206" t="b">
-        <v>0</v>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -17055,8 +17465,10 @@
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="b">
-        <v>1</v>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -17138,8 +17550,10 @@
       <c r="R208" t="n">
         <v>0.9818072770891644</v>
       </c>
-      <c r="S208" t="b">
-        <v>0</v>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -17217,8 +17631,10 @@
       <c r="R209" t="n">
         <v>0.008996401439424262</v>
       </c>
-      <c r="S209" t="b">
-        <v>1</v>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -17296,8 +17712,10 @@
       <c r="R210" t="n">
         <v>0.008996401439424262</v>
       </c>
-      <c r="S210" t="b">
-        <v>1</v>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -17375,8 +17793,10 @@
       <c r="R211" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="S211" t="b">
-        <v>0</v>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -17454,8 +17874,10 @@
       <c r="R212" t="n">
         <v>0.003598560575769683</v>
       </c>
-      <c r="S212" t="b">
-        <v>0</v>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -17533,8 +17955,10 @@
       <c r="R213" t="n">
         <v>0.5177928828468612</v>
       </c>
-      <c r="S213" t="b">
-        <v>1</v>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -17612,8 +18036,10 @@
       <c r="R214" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S214" t="b">
-        <v>0</v>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -17695,8 +18121,10 @@
       <c r="R215" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S215" t="b">
-        <v>1</v>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -17778,8 +18206,10 @@
       <c r="R216" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S216" t="b">
-        <v>1</v>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -17861,8 +18291,10 @@
       <c r="R217" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S217" t="b">
-        <v>1</v>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -17944,8 +18376,10 @@
       <c r="R218" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="S218" t="b">
-        <v>0</v>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -18027,8 +18461,10 @@
       <c r="R219" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S219" t="b">
-        <v>0</v>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -18110,8 +18546,10 @@
       <c r="R220" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S220" t="b">
-        <v>0</v>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -18193,8 +18631,10 @@
       <c r="R221" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S221" t="b">
-        <v>0</v>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -18276,8 +18716,10 @@
       <c r="R222" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="S222" t="b">
-        <v>1</v>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -18359,8 +18801,10 @@
       <c r="R223" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S223" t="b">
-        <v>1</v>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -18442,8 +18886,10 @@
       <c r="R224" t="n">
         <v>0.9952019192323071</v>
       </c>
-      <c r="S224" t="b">
-        <v>0</v>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -18525,8 +18971,10 @@
       <c r="R225" t="n">
         <v>0.3132746901239504</v>
       </c>
-      <c r="S225" t="b">
-        <v>0</v>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -18608,8 +19056,10 @@
       <c r="R226" t="n">
         <v>0.3132746901239504</v>
       </c>
-      <c r="S226" t="b">
-        <v>0</v>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -18691,8 +19141,10 @@
       <c r="R227" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="S227" t="b">
-        <v>0</v>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -18774,8 +19226,10 @@
       <c r="R228" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="S228" t="b">
-        <v>0</v>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -18857,8 +19311,10 @@
       <c r="R229" t="n">
         <v>0.03098760495801678</v>
       </c>
-      <c r="S229" t="b">
-        <v>0</v>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -18940,8 +19396,10 @@
       <c r="R230" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S230" t="b">
-        <v>0</v>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -19023,8 +19481,10 @@
       <c r="R231" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S231" t="b">
-        <v>0</v>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -19106,8 +19566,10 @@
       <c r="R232" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S232" t="b">
-        <v>0</v>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -19189,8 +19651,10 @@
       <c r="R233" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S233" t="b">
-        <v>0</v>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -19272,8 +19736,10 @@
       <c r="R234" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S234" t="b">
-        <v>0</v>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -19355,8 +19821,10 @@
       <c r="R235" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S235" t="b">
-        <v>0</v>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -19438,8 +19906,10 @@
       <c r="R236" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S236" t="b">
-        <v>0</v>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -19521,8 +19991,10 @@
       <c r="R237" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S237" t="b">
-        <v>0</v>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -19604,8 +20076,10 @@
       <c r="R238" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S238" t="b">
-        <v>0</v>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -19687,8 +20161,10 @@
       <c r="R239" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S239" t="b">
-        <v>0</v>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -19770,8 +20246,10 @@
       <c r="R240" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S240" t="b">
-        <v>0</v>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -19853,8 +20331,10 @@
       <c r="R241" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S241" t="b">
-        <v>0</v>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -19936,8 +20416,10 @@
       <c r="R242" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S242" t="b">
-        <v>0</v>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -20003,8 +20485,10 @@
       <c r="R243" t="n">
         <v>0</v>
       </c>
-      <c r="S243" t="b">
-        <v>1</v>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -20082,8 +20566,10 @@
       <c r="R244" t="n">
         <v>0.3268692522990804</v>
       </c>
-      <c r="S244" t="b">
-        <v>1</v>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -20161,8 +20647,10 @@
       <c r="R245" t="n">
         <v>0.09476209516193523</v>
       </c>
-      <c r="S245" t="b">
-        <v>1</v>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -20240,8 +20728,10 @@
       <c r="R246" t="n">
         <v>0.1359456217512994</v>
       </c>
-      <c r="S246" t="b">
-        <v>1</v>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -20319,8 +20809,10 @@
       <c r="R247" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S247" t="b">
-        <v>0</v>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -20398,8 +20890,10 @@
       <c r="R248" t="n">
         <v>0.1551379448220712</v>
       </c>
-      <c r="S248" t="b">
-        <v>0</v>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -20477,8 +20971,10 @@
       <c r="R249" t="n">
         <v>0.183326669332267</v>
       </c>
-      <c r="S249" t="b">
-        <v>0</v>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -20556,8 +21052,10 @@
       <c r="R250" t="n">
         <v>0.8632546981207517</v>
       </c>
-      <c r="S250" t="b">
-        <v>0</v>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -20635,8 +21133,10 @@
       <c r="R251" t="n">
         <v>0.4150339864054379</v>
       </c>
-      <c r="S251" t="b">
-        <v>0</v>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -20714,8 +21214,10 @@
       <c r="R252" t="n">
         <v>0.2634946021591363</v>
       </c>
-      <c r="S252" t="b">
-        <v>1</v>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -20793,8 +21295,10 @@
       <c r="R253" t="n">
         <v>0.2846861255497801</v>
       </c>
-      <c r="S253" t="b">
-        <v>1</v>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -20872,8 +21376,10 @@
       <c r="R254" t="n">
         <v>0.8632546981207517</v>
       </c>
-      <c r="S254" t="b">
-        <v>1</v>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -20951,8 +21457,10 @@
       <c r="R255" t="n">
         <v>0.4150339864054379</v>
       </c>
-      <c r="S255" t="b">
-        <v>1</v>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -21030,8 +21538,10 @@
       <c r="R256" t="n">
         <v>0.2634946021591363</v>
       </c>
-      <c r="S256" t="b">
-        <v>0</v>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -21109,8 +21619,10 @@
       <c r="R257" t="n">
         <v>0.2846861255497801</v>
       </c>
-      <c r="S257" t="b">
-        <v>0</v>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -21188,8 +21700,10 @@
       <c r="R258" t="n">
         <v>0.9960015993602559</v>
       </c>
-      <c r="S258" t="b">
-        <v>0</v>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -21267,8 +21781,10 @@
       <c r="R259" t="n">
         <v>0.1637345061975209</v>
       </c>
-      <c r="S259" t="b">
-        <v>0</v>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -21346,8 +21862,10 @@
       <c r="R260" t="n">
         <v>0.1637345061975209</v>
       </c>
-      <c r="S260" t="b">
-        <v>0</v>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -21425,8 +21943,10 @@
       <c r="R261" t="n">
         <v>0.03418632546981204</v>
       </c>
-      <c r="S261" t="b">
-        <v>0</v>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -21504,8 +22024,10 @@
       <c r="R262" t="n">
         <v>0.04878048780487809</v>
       </c>
-      <c r="S262" t="b">
-        <v>0</v>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -21587,8 +22109,10 @@
       <c r="R263" t="n">
         <v>0.5771691323470611</v>
       </c>
-      <c r="S263" t="b">
-        <v>1</v>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -21670,8 +22194,10 @@
       <c r="R264" t="n">
         <v>0.5771691323470611</v>
       </c>
-      <c r="S264" t="b">
-        <v>1</v>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -21749,8 +22275,10 @@
       <c r="R265" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S265" t="b">
-        <v>0</v>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -21832,8 +22360,10 @@
       <c r="R266" t="n">
         <v>0.3052778888444622</v>
       </c>
-      <c r="S266" t="b">
-        <v>1</v>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -21915,8 +22445,10 @@
       <c r="R267" t="n">
         <v>0.0177928828468612</v>
       </c>
-      <c r="S267" t="b">
-        <v>1</v>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -21994,8 +22526,10 @@
       <c r="R268" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S268" t="b">
-        <v>0</v>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -22077,8 +22611,10 @@
       <c r="R269" t="n">
         <v>0.273890443822471</v>
       </c>
-      <c r="S269" t="b">
-        <v>1</v>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -22160,8 +22696,10 @@
       <c r="R270" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S270" t="b">
-        <v>1</v>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -22243,8 +22781,10 @@
       <c r="R271" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S271" t="b">
-        <v>1</v>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -22326,8 +22866,10 @@
       <c r="R272" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S272" t="b">
-        <v>1</v>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -22409,8 +22951,10 @@
       <c r="R273" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S273" t="b">
-        <v>1</v>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -22492,8 +23036,10 @@
       <c r="R274" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S274" t="b">
-        <v>1</v>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -22575,8 +23121,10 @@
       <c r="R275" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="S275" t="b">
-        <v>0</v>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -22658,8 +23206,10 @@
       <c r="R276" t="n">
         <v>0.2526989204318273</v>
       </c>
-      <c r="S276" t="b">
-        <v>0</v>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -22741,8 +23291,10 @@
       <c r="R277" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S277" t="b">
-        <v>0</v>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -22824,8 +23376,10 @@
       <c r="R278" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S278" t="b">
-        <v>0</v>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -22907,8 +23461,10 @@
       <c r="R279" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="S279" t="b">
-        <v>0</v>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -22990,8 +23546,10 @@
       <c r="R280" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="S280" t="b">
-        <v>0</v>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -23073,8 +23631,10 @@
       <c r="R281" t="n">
         <v>0.2157137145141943</v>
       </c>
-      <c r="S281" t="b">
-        <v>0</v>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -23156,8 +23716,10 @@
       <c r="R282" t="n">
         <v>0.0005997600959616323</v>
       </c>
-      <c r="S282" t="b">
-        <v>0</v>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -23239,8 +23801,10 @@
       <c r="R283" t="n">
         <v>0.0005997600959616323</v>
       </c>
-      <c r="S283" t="b">
-        <v>0</v>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -23322,8 +23886,10 @@
       <c r="R284" t="n">
         <v>0.0005997600959616323</v>
       </c>
-      <c r="S284" t="b">
-        <v>0</v>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -23405,8 +23971,10 @@
       <c r="R285" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S285" t="b">
-        <v>0</v>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -23488,8 +24056,10 @@
       <c r="R286" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S286" t="b">
-        <v>0</v>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -23571,8 +24141,10 @@
       <c r="R287" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S287" t="b">
-        <v>0</v>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -23654,8 +24226,10 @@
       <c r="R288" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S288" t="b">
-        <v>0</v>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -23737,8 +24311,10 @@
       <c r="R289" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S289" t="b">
-        <v>0</v>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -23820,8 +24396,10 @@
       <c r="R290" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S290" t="b">
-        <v>0</v>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -23903,8 +24481,10 @@
       <c r="R291" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S291" t="b">
-        <v>0</v>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -23986,8 +24566,10 @@
       <c r="R292" t="n">
         <v>0.2469012395041983</v>
       </c>
-      <c r="S292" t="b">
-        <v>1</v>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -24069,8 +24651,10 @@
       <c r="R293" t="n">
         <v>0.9958016793282687</v>
       </c>
-      <c r="S293" t="b">
-        <v>0</v>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -24156,8 +24740,10 @@
       <c r="R294" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S294" t="b">
-        <v>1</v>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -24243,8 +24829,10 @@
       <c r="R295" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S295" t="b">
-        <v>1</v>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -24330,8 +24918,10 @@
       <c r="R296" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S296" t="b">
-        <v>1</v>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -24417,8 +25007,10 @@
       <c r="R297" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="S297" t="b">
-        <v>1</v>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -24504,8 +25096,10 @@
       <c r="R298" t="n">
         <v>0.5851659336265493</v>
       </c>
-      <c r="S298" t="b">
-        <v>0</v>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -24591,8 +25185,10 @@
       <c r="R299" t="n">
         <v>0.7782886845261895</v>
       </c>
-      <c r="S299" t="b">
-        <v>0</v>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -24678,8 +25274,10 @@
       <c r="R300" t="n">
         <v>0.9788084766093562</v>
       </c>
-      <c r="S300" t="b">
-        <v>1</v>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -24765,8 +25363,10 @@
       <c r="R301" t="n">
         <v>0.4680127948820472</v>
       </c>
-      <c r="S301" t="b">
-        <v>1</v>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -24852,8 +25452,10 @@
       <c r="R302" t="n">
         <v>0.4680127948820472</v>
       </c>
-      <c r="S302" t="b">
-        <v>1</v>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -24935,8 +25537,10 @@
       <c r="R303" t="n">
         <v>0.975609756097561</v>
       </c>
-      <c r="S303" t="b">
-        <v>0</v>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -25018,8 +25622,10 @@
       <c r="R304" t="n">
         <v>0.5429828068772491</v>
       </c>
-      <c r="S304" t="b">
-        <v>0</v>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -25101,8 +25707,10 @@
       <c r="R305" t="n">
         <v>0.5287884846061575</v>
       </c>
-      <c r="S305" t="b">
-        <v>0</v>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -25184,8 +25792,10 @@
       <c r="R306" t="n">
         <v>0.6183526589364254</v>
       </c>
-      <c r="S306" t="b">
-        <v>1</v>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -25267,8 +25877,10 @@
       <c r="R307" t="n">
         <v>0.3788484606157537</v>
       </c>
-      <c r="S307" t="b">
-        <v>1</v>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -25350,8 +25962,10 @@
       <c r="R308" t="n">
         <v>0.832467013194722</v>
       </c>
-      <c r="S308" t="b">
-        <v>1</v>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -25433,8 +26047,10 @@
       <c r="R309" t="n">
         <v>0.6259496201519392</v>
       </c>
-      <c r="S309" t="b">
-        <v>1</v>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -25516,8 +26132,10 @@
       <c r="R310" t="n">
         <v>0.9912035185925629</v>
       </c>
-      <c r="S310" t="b">
-        <v>0</v>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -25599,8 +26217,10 @@
       <c r="R311" t="n">
         <v>0.7275089964014394</v>
       </c>
-      <c r="S311" t="b">
-        <v>0</v>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -25682,8 +26302,10 @@
       <c r="R312" t="n">
         <v>0.782686925229908</v>
       </c>
-      <c r="S312" t="b">
-        <v>0</v>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -25769,8 +26391,10 @@
       <c r="R313" t="n">
         <v>0.7389044382247101</v>
       </c>
-      <c r="S313" t="b">
-        <v>1</v>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -25848,8 +26472,10 @@
       <c r="R314" t="n">
         <v>0.9984006397441023</v>
       </c>
-      <c r="S314" t="b">
-        <v>0</v>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -25927,8 +26553,10 @@
       <c r="R315" t="n">
         <v>0.7660935625749701</v>
       </c>
-      <c r="S315" t="b">
-        <v>0</v>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -26010,8 +26638,10 @@
       <c r="R316" t="n">
         <v>0.1259496201519392</v>
       </c>
-      <c r="S316" t="b">
-        <v>1</v>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -26093,8 +26723,10 @@
       <c r="R317" t="n">
         <v>0.1183526589364254</v>
       </c>
-      <c r="S317" t="b">
-        <v>1</v>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -26172,8 +26804,10 @@
       <c r="R318" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S318" t="b">
-        <v>0</v>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -26251,8 +26885,10 @@
       <c r="R319" t="n">
         <v>0.3422630947620952</v>
       </c>
-      <c r="S319" t="b">
-        <v>0</v>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -26330,8 +26966,10 @@
       <c r="R320" t="n">
         <v>0.3310675729708117</v>
       </c>
-      <c r="S320" t="b">
-        <v>0</v>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -26409,8 +27047,10 @@
       <c r="R321" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="S321" t="b">
-        <v>1</v>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="322">
@@ -26488,8 +27128,10 @@
       <c r="R322" t="n">
         <v>0.6457417033186725</v>
       </c>
-      <c r="S322" t="b">
-        <v>1</v>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="323">
@@ -26567,8 +27209,10 @@
       <c r="R323" t="n">
         <v>0.3272690923630548</v>
       </c>
-      <c r="S323" t="b">
-        <v>1</v>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -26650,8 +27294,10 @@
       <c r="R324" t="n">
         <v>0.7135145941623351</v>
       </c>
-      <c r="S324" t="b">
-        <v>0</v>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="325">
@@ -26737,8 +27383,10 @@
       <c r="R325" t="n">
         <v>0.9796081567373051</v>
       </c>
-      <c r="S325" t="b">
-        <v>1</v>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="326">
@@ -26824,8 +27472,10 @@
       <c r="R326" t="n">
         <v>0.1319472211115553</v>
       </c>
-      <c r="S326" t="b">
-        <v>1</v>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="327">
@@ -26907,8 +27557,10 @@
       <c r="R327" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S327" t="b">
-        <v>0</v>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="328">
@@ -26990,8 +27642,10 @@
       <c r="R328" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="S328" t="b">
-        <v>1</v>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="329">
@@ -27073,8 +27727,10 @@
       <c r="R329" t="n">
         <v>0.975609756097561</v>
       </c>
-      <c r="S329" t="b">
-        <v>1</v>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="330">
@@ -27156,8 +27812,10 @@
       <c r="R330" t="n">
         <v>0.444422231107557</v>
       </c>
-      <c r="S330" t="b">
-        <v>1</v>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -27235,8 +27893,10 @@
       <c r="R331" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S331" t="b">
-        <v>0</v>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="332">
@@ -27314,8 +27974,10 @@
       <c r="R332" t="n">
         <v>0.7435025989604158</v>
       </c>
-      <c r="S332" t="b">
-        <v>0</v>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="333">
@@ -27393,8 +28055,10 @@
       <c r="R333" t="n">
         <v>0.7692922830867652</v>
       </c>
-      <c r="S333" t="b">
-        <v>0</v>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="334">
@@ -27472,8 +28136,10 @@
       <c r="R334" t="n">
         <v>0.788484606157537</v>
       </c>
-      <c r="S334" t="b">
-        <v>0</v>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="335">
@@ -27551,8 +28217,10 @@
       <c r="R335" t="n">
         <v>0.816673330667733</v>
       </c>
-      <c r="S335" t="b">
-        <v>0</v>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="336">
@@ -27630,8 +28298,10 @@
       <c r="R336" t="n">
         <v>0.7860855657736905</v>
       </c>
-      <c r="S336" t="b">
-        <v>1</v>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="337">
@@ -27713,8 +28383,10 @@
       <c r="R337" t="n">
         <v>0.9978008796481408</v>
       </c>
-      <c r="S337" t="b">
-        <v>0</v>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -27796,8 +28468,10 @@
       <c r="R338" t="n">
         <v>0.6483406637345062</v>
       </c>
-      <c r="S338" t="b">
-        <v>0</v>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="339">
@@ -27879,8 +28553,10 @@
       <c r="R339" t="n">
         <v>0.6285485805677729</v>
       </c>
-      <c r="S339" t="b">
-        <v>1</v>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -27962,8 +28638,10 @@
       <c r="R340" t="n">
         <v>0.9970011995201919</v>
       </c>
-      <c r="S340" t="b">
-        <v>0</v>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="341">
@@ -28045,8 +28723,10 @@
       <c r="R341" t="n">
         <v>0.5969612155137944</v>
       </c>
-      <c r="S341" t="b">
-        <v>0</v>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="342">
@@ -28128,8 +28808,10 @@
       <c r="R342" t="n">
         <v>0.5969612155137944</v>
       </c>
-      <c r="S342" t="b">
-        <v>0</v>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="343">
@@ -28211,8 +28893,10 @@
       <c r="R343" t="n">
         <v>0.1221511395441823</v>
       </c>
-      <c r="S343" t="b">
-        <v>0</v>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="344">
@@ -28294,8 +28978,10 @@
       <c r="R344" t="n">
         <v>0.1303478608556577</v>
       </c>
-      <c r="S344" t="b">
-        <v>0</v>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="345">
@@ -28377,8 +29063,10 @@
       <c r="R345" t="n">
         <v>0.7269092363054779</v>
       </c>
-      <c r="S345" t="b">
-        <v>1</v>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="346">
@@ -28456,8 +29144,10 @@
       <c r="R346" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="S346" t="b">
-        <v>0</v>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="347">
@@ -28535,8 +29225,10 @@
       <c r="R347" t="n">
         <v>0.8234706117552979</v>
       </c>
-      <c r="S347" t="b">
-        <v>1</v>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="348">
@@ -28614,8 +29306,10 @@
       <c r="R348" t="n">
         <v>0.875249900039984</v>
       </c>
-      <c r="S348" t="b">
-        <v>1</v>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="349">
@@ -28697,8 +29391,10 @@
       <c r="R349" t="n">
         <v>0.2161135545781687</v>
       </c>
-      <c r="S349" t="b">
-        <v>0</v>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="350">
@@ -28776,8 +29472,10 @@
       <c r="R350" t="n">
         <v>0.9808076769292283</v>
       </c>
-      <c r="S350" t="b">
-        <v>1</v>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>Strong disagree</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -28855,8 +29553,10 @@
       <c r="R351" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="S351" t="b">
-        <v>0</v>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="352">
@@ -28934,8 +29634,10 @@
       <c r="R352" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="S352" t="b">
-        <v>0</v>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="353">
@@ -29013,8 +29715,10 @@
       <c r="R353" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="S353" t="b">
-        <v>0</v>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="354">
@@ -29092,8 +29796,10 @@
       <c r="R354" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="S354" t="b">
-        <v>0</v>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="355">
@@ -29171,8 +29877,10 @@
       <c r="R355" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="S355" t="b">
-        <v>1</v>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="356">
@@ -29250,8 +29958,10 @@
       <c r="R356" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="S356" t="b">
-        <v>1</v>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="357">
@@ -29329,8 +30039,10 @@
       <c r="R357" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="S357" t="b">
-        <v>1</v>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -29408,8 +30120,10 @@
       <c r="R358" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="S358" t="b">
-        <v>1</v>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="359">
@@ -29487,8 +30201,10 @@
       <c r="R359" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="S359" t="b">
-        <v>1</v>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="360">
@@ -29566,8 +30282,10 @@
       <c r="R360" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="S360" t="b">
-        <v>1</v>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="361">
@@ -29649,8 +30367,10 @@
       <c r="R361" t="n">
         <v>0.8872451019592164</v>
       </c>
-      <c r="S361" t="b">
-        <v>1</v>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -29732,8 +30452,10 @@
       <c r="R362" t="n">
         <v>0.9932027189124351</v>
       </c>
-      <c r="S362" t="b">
-        <v>0</v>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="363">
@@ -29815,8 +30537,10 @@
       <c r="R363" t="n">
         <v>0.998000799680128</v>
       </c>
-      <c r="S363" t="b">
-        <v>0</v>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -29898,8 +30622,10 @@
       <c r="R364" t="n">
         <v>0.9778088764494203</v>
       </c>
-      <c r="S364" t="b">
-        <v>0</v>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="365">
@@ -29981,8 +30707,10 @@
       <c r="R365" t="n">
         <v>0.816673330667733</v>
       </c>
-      <c r="S365" t="b">
-        <v>0</v>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="366">
@@ -30064,8 +30792,10 @@
       <c r="R366" t="n">
         <v>0.07996801279488208</v>
       </c>
-      <c r="S366" t="b">
-        <v>0</v>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="367">
@@ -30147,8 +30877,10 @@
       <c r="R367" t="n">
         <v>0.07996801279488208</v>
       </c>
-      <c r="S367" t="b">
-        <v>0</v>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="368">
@@ -30214,8 +30946,10 @@
       <c r="R368" t="n">
         <v>0</v>
       </c>
-      <c r="S368" t="b">
-        <v>1</v>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -30293,8 +31027,10 @@
       <c r="R369" t="n">
         <v>0.8498600559776089</v>
       </c>
-      <c r="S369" t="b">
-        <v>0</v>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>Weak agree</t>
+        </is>
       </c>
     </row>
     <row r="370">
@@ -30372,8 +31108,10 @@
       <c r="R370" t="n">
         <v>0.4194322271091563</v>
       </c>
-      <c r="S370" t="b">
-        <v>1</v>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="371">
@@ -30451,8 +31189,10 @@
       <c r="R371" t="n">
         <v>0.9978008796481408</v>
       </c>
-      <c r="S371" t="b">
-        <v>0</v>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>Strong agree</t>
+        </is>
       </c>
     </row>
     <row r="372">
@@ -30530,8 +31270,10 @@
       <c r="R372" t="n">
         <v>0.0177928828468612</v>
       </c>
-      <c r="S372" t="b">
-        <v>1</v>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
     <row r="373">
@@ -30609,8 +31351,10 @@
       <c r="R373" t="n">
         <v>0.0177928828468612</v>
       </c>
-      <c r="S373" t="b">
-        <v>1</v>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>Weak disagree</t>
+        </is>
       </c>
     </row>
   </sheetData>
